--- a/input_data/admin_data/ECU/_clean/total-pre-ECU.xlsx
+++ b/input_data/admin_data/ECU/_clean/total-pre-ECU.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="97">
   <si>
     <t>year</t>
   </si>
@@ -40,6 +40,270 @@
   </si>
   <si>
     <t>postax</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>ECU</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>component</t>
+  </si>
+  <si>
+    <t>postax</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>ECU</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>component</t>
+  </si>
+  <si>
+    <t>postax</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>ECU</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>component</t>
+  </si>
+  <si>
+    <t>postax</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>ECU</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>component</t>
+  </si>
+  <si>
+    <t>postax</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>bracketavg</t>
@@ -93,22 +357,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
@@ -116,7 +380,7 @@
         <v>2008</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1">
         <v>27.642103216567037</v>
@@ -125,7 +389,7 @@
         <v>0.99942106008529663</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F2" s="1">
         <v>6201.1068160713085</v>
@@ -134,14 +398,14 @@
     <row r="3">
       <c r="A3" s="1"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1">
         <v>0.99971026182174683</v>
       </c>
       <c r="E3" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="F3" s="1">
         <v>11701.011533552277</v>
@@ -150,14 +414,14 @@
     <row r="4">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1">
         <v>0.99994170665740967</v>
       </c>
       <c r="E4" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="F4" s="1">
         <v>34409.242584</v>
@@ -166,14 +430,14 @@
     <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1">
         <v>0.99997061491012573</v>
       </c>
       <c r="E5" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="F5" s="1">
         <v>44915.427675000006</v>
@@ -182,14 +446,14 @@
     <row r="6">
       <c r="A6" s="1"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1">
         <v>0.99999374151229858</v>
       </c>
       <c r="E6" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F6" s="1">
         <v>102223.13359500001</v>
@@ -198,14 +462,14 @@
     <row r="7">
       <c r="A7" s="1"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1">
         <v>0.99999666213989258</v>
       </c>
       <c r="E7" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="F7" s="1">
         <v>134221.16051399999</v>
@@ -214,14 +478,14 @@
     <row r="8">
       <c r="A8" s="1"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1">
         <v>0.99999898672103882</v>
       </c>
       <c r="E8" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="F8" s="1">
         <v>393989.84531999996</v>
@@ -230,14 +494,14 @@
     <row r="9">
       <c r="A9" s="1"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1">
         <v>0.99999946355819702</v>
       </c>
       <c r="E9" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="F9" s="1">
         <v>2327811.3491759994</v>
@@ -254,22 +518,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="F1" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2">
@@ -277,7 +541,7 @@
         <v>2009</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="C2" s="1">
         <v>27.123078602786062</v>
@@ -286,7 +550,7 @@
         <v>0.99941641092300415</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="F2" s="1">
         <v>7427.2634220259715</v>
@@ -295,14 +559,14 @@
     <row r="3">
       <c r="A3" s="1"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1">
         <v>0.99970799684524536</v>
       </c>
       <c r="E3" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="F3" s="1">
         <v>13488.39384913874</v>
@@ -311,14 +575,14 @@
     <row r="4">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1">
         <v>0.99994122982025146</v>
       </c>
       <c r="E4" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="F4" s="1">
         <v>38196.156768000001</v>
@@ -327,14 +591,14 @@
     <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1">
         <v>0.99997037649154663</v>
       </c>
       <c r="E5" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="F5" s="1">
         <v>49205.200968000005</v>
@@ -343,14 +607,14 @@
     <row r="6">
       <c r="A6" s="1"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1">
         <v>0.99999368190765381</v>
       </c>
       <c r="E6" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="F6" s="1">
         <v>118355.55177599999</v>
@@ -359,14 +623,14 @@
     <row r="7">
       <c r="A7" s="1"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1">
         <v>0.9999966025352478</v>
       </c>
       <c r="E7" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="F7" s="1">
         <v>158940.49248000002</v>
@@ -375,14 +639,14 @@
     <row r="8">
       <c r="A8" s="1"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1">
         <v>0.99999892711639404</v>
       </c>
       <c r="E8" t="s">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="F8" s="1">
         <v>479378.85349199997</v>
@@ -391,14 +655,14 @@
     <row r="9">
       <c r="A9" s="1"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1">
         <v>0.99999946355819702</v>
       </c>
       <c r="E9" t="s">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="F9" s="1">
         <v>3192587.0213159998</v>
@@ -415,22 +679,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="F1" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2">
@@ -438,7 +702,7 @@
         <v>2010</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="C2" s="1">
         <v>29.466916212687494</v>
@@ -447,7 +711,7 @@
         <v>0.99941170215606689</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="F2" s="1">
         <v>7514.7884521280221</v>
@@ -456,14 +720,14 @@
     <row r="3">
       <c r="A3" s="1"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1">
         <v>0.99970561265945435</v>
       </c>
       <c r="E3" t="s">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="F3" s="1">
         <v>13747.391606108247</v>
@@ -472,14 +736,14 @@
     <row r="4">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1">
         <v>0.99994075298309326</v>
       </c>
       <c r="E4" t="s">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="F4" s="1">
         <v>38292.759681000003</v>
@@ -488,14 +752,14 @@
     <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1">
         <v>0.99997013807296753</v>
       </c>
       <c r="E5" t="s">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="F5" s="1">
         <v>49642.068630000016</v>
@@ -504,14 +768,14 @@
     <row r="6">
       <c r="A6" s="1"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1">
         <v>0.99999362230300903</v>
       </c>
       <c r="E6" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="F6" s="1">
         <v>118746.68454000002</v>
@@ -520,14 +784,14 @@
     <row r="7">
       <c r="A7" s="1"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1">
         <v>0.9999966025352478</v>
       </c>
       <c r="E7" t="s">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="F7" s="1">
         <v>148805.54350200001</v>
@@ -536,14 +800,14 @@
     <row r="8">
       <c r="A8" s="1"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1">
         <v>0.99999892711639404</v>
       </c>
       <c r="E8" t="s">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="F8" s="1">
         <v>398746.96567200008</v>
@@ -552,14 +816,14 @@
     <row r="9">
       <c r="A9" s="1"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1">
         <v>0.99999946355819702</v>
       </c>
       <c r="E9" t="s">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="F9" s="1">
         <v>1848757.1221680001</v>
@@ -576,22 +840,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>86</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>87</v>
       </c>
       <c r="F1" t="s">
-        <v>8</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
@@ -599,7 +863,7 @@
         <v>2011</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="C2" s="1">
         <v>33.465564727783203</v>
@@ -608,7 +872,7 @@
         <v>0.99940687417984009</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
       <c r="F2" s="1">
         <v>10339.130287100314</v>
@@ -617,14 +881,14 @@
     <row r="3">
       <c r="A3" s="1"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1">
         <v>0.99970322847366333</v>
       </c>
       <c r="E3" t="s">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="F3" s="1">
         <v>15366.538025025684</v>
@@ -633,14 +897,14 @@
     <row r="4">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1">
         <v>0.99994027614593506</v>
       </c>
       <c r="E4" t="s">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="F4" s="1">
         <v>37523.415000000008</v>
@@ -649,14 +913,14 @@
     <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1">
         <v>0.99996989965438843</v>
       </c>
       <c r="E5" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
       <c r="F5" s="1">
         <v>45908.899999999994</v>
@@ -665,14 +929,14 @@
     <row r="6">
       <c r="A6" s="1"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1">
         <v>0.99999362230300903</v>
       </c>
       <c r="E6" t="s">
-        <v>3</v>
+        <v>92</v>
       </c>
       <c r="F6" s="1">
         <v>110935.78200000001</v>
@@ -681,14 +945,14 @@
     <row r="7">
       <c r="A7" s="1"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1">
         <v>0.99999654293060303</v>
       </c>
       <c r="E7" t="s">
-        <v>3</v>
+        <v>93</v>
       </c>
       <c r="F7" s="1">
         <v>136489.69499999998</v>
@@ -697,14 +961,14 @@
     <row r="8">
       <c r="A8" s="1"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1">
         <v>0.99999892711639404</v>
       </c>
       <c r="E8" t="s">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="F8" s="1">
         <v>407213.54200000002</v>
@@ -713,14 +977,14 @@
     <row r="9">
       <c r="A9" s="1"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1">
         <v>0.99999946355819702</v>
       </c>
       <c r="E9" t="s">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="F9" s="1">
         <v>2720421.3669999996</v>

--- a/input_data/admin_data/ECU/_clean/total-pre-ECU.xlsx
+++ b/input_data/admin_data/ECU/_clean/total-pre-ECU.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="97">
   <si>
     <t>year</t>
   </si>
@@ -357,22 +357,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="C1" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="D1" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="E1" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="F1" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
@@ -380,7 +380,7 @@
         <v>2008</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="C2" s="1">
         <v>27.642103216567037</v>
@@ -389,7 +389,7 @@
         <v>0.99942106008529663</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="F2" s="1">
         <v>6201.1068160713085</v>
@@ -398,14 +398,14 @@
     <row r="3">
       <c r="A3" s="1"/>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1">
         <v>0.99971026182174683</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="F3" s="1">
         <v>11701.011533552277</v>
@@ -414,14 +414,14 @@
     <row r="4">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1">
         <v>0.99994170665740967</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="F4" s="1">
         <v>34409.242584</v>
@@ -430,14 +430,14 @@
     <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1">
         <v>0.99997061491012573</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="F5" s="1">
         <v>44915.427675000006</v>
@@ -446,14 +446,14 @@
     <row r="6">
       <c r="A6" s="1"/>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1">
         <v>0.99999374151229858</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="F6" s="1">
         <v>102223.13359500001</v>
@@ -462,14 +462,14 @@
     <row r="7">
       <c r="A7" s="1"/>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1">
         <v>0.99999666213989258</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="F7" s="1">
         <v>134221.16051399999</v>
@@ -478,14 +478,14 @@
     <row r="8">
       <c r="A8" s="1"/>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1">
         <v>0.99999898672103882</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="F8" s="1">
         <v>393989.84531999996</v>
@@ -494,14 +494,14 @@
     <row r="9">
       <c r="A9" s="1"/>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1">
         <v>0.99999946355819702</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="F9" s="1">
         <v>2327811.3491759994</v>
@@ -518,22 +518,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="B1" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="C1" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="D1" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="E1" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="F1" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
@@ -541,7 +541,7 @@
         <v>2009</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="C2" s="1">
         <v>27.123078602786062</v>
@@ -550,7 +550,7 @@
         <v>0.99941641092300415</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F2" s="1">
         <v>7427.2634220259715</v>
@@ -559,14 +559,14 @@
     <row r="3">
       <c r="A3" s="1"/>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1">
         <v>0.99970799684524536</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="F3" s="1">
         <v>13488.39384913874</v>
@@ -575,14 +575,14 @@
     <row r="4">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1">
         <v>0.99994122982025146</v>
       </c>
       <c r="E4" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="F4" s="1">
         <v>38196.156768000001</v>
@@ -591,14 +591,14 @@
     <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1">
         <v>0.99997037649154663</v>
       </c>
       <c r="E5" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="F5" s="1">
         <v>49205.200968000005</v>
@@ -607,14 +607,14 @@
     <row r="6">
       <c r="A6" s="1"/>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>95</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1">
         <v>0.99999368190765381</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="F6" s="1">
         <v>118355.55177599999</v>
@@ -623,14 +623,14 @@
     <row r="7">
       <c r="A7" s="1"/>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1">
         <v>0.9999966025352478</v>
       </c>
       <c r="E7" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="F7" s="1">
         <v>158940.49248000002</v>
@@ -639,14 +639,14 @@
     <row r="8">
       <c r="A8" s="1"/>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1">
         <v>0.99999892711639404</v>
       </c>
       <c r="E8" t="s">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="F8" s="1">
         <v>479378.85349199997</v>
@@ -655,14 +655,14 @@
     <row r="9">
       <c r="A9" s="1"/>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1">
         <v>0.99999946355819702</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="F9" s="1">
         <v>3192587.0213159998</v>
@@ -679,22 +679,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="C1" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="D1" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="E1" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="F1" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
@@ -702,7 +702,7 @@
         <v>2010</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="C2" s="1">
         <v>29.466916212687494</v>
@@ -711,7 +711,7 @@
         <v>0.99941170215606689</v>
       </c>
       <c r="E2" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="F2" s="1">
         <v>7514.7884521280221</v>
@@ -720,14 +720,14 @@
     <row r="3">
       <c r="A3" s="1"/>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1">
         <v>0.99970561265945435</v>
       </c>
       <c r="E3" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="F3" s="1">
         <v>13747.391606108247</v>
@@ -736,14 +736,14 @@
     <row r="4">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1">
         <v>0.99994075298309326</v>
       </c>
       <c r="E4" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="F4" s="1">
         <v>38292.759681000003</v>
@@ -752,14 +752,14 @@
     <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1">
         <v>0.99997013807296753</v>
       </c>
       <c r="E5" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="F5" s="1">
         <v>49642.068630000016</v>
@@ -768,14 +768,14 @@
     <row r="6">
       <c r="A6" s="1"/>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1">
         <v>0.99999362230300903</v>
       </c>
       <c r="E6" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F6" s="1">
         <v>118746.68454000002</v>
@@ -784,14 +784,14 @@
     <row r="7">
       <c r="A7" s="1"/>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1">
         <v>0.9999966025352478</v>
       </c>
       <c r="E7" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="F7" s="1">
         <v>148805.54350200001</v>
@@ -800,14 +800,14 @@
     <row r="8">
       <c r="A8" s="1"/>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1">
         <v>0.99999892711639404</v>
       </c>
       <c r="E8" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="F8" s="1">
         <v>398746.96567200008</v>
@@ -816,14 +816,14 @@
     <row r="9">
       <c r="A9" s="1"/>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1">
         <v>0.99999946355819702</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="F9" s="1">
         <v>1848757.1221680001</v>
@@ -881,14 +881,14 @@
     <row r="3">
       <c r="A3" s="1"/>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1">
         <v>0.99970322847366333</v>
       </c>
       <c r="E3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F3" s="1">
         <v>15366.538025025684</v>
@@ -897,14 +897,14 @@
     <row r="4">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1">
         <v>0.99994027614593506</v>
       </c>
       <c r="E4" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F4" s="1">
         <v>37523.415000000008</v>
@@ -913,14 +913,14 @@
     <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1">
         <v>0.99996989965438843</v>
       </c>
       <c r="E5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F5" s="1">
         <v>45908.899999999994</v>
@@ -929,14 +929,14 @@
     <row r="6">
       <c r="A6" s="1"/>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1">
         <v>0.99999362230300903</v>
       </c>
       <c r="E6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F6" s="1">
         <v>110935.78200000001</v>
@@ -945,14 +945,14 @@
     <row r="7">
       <c r="A7" s="1"/>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1">
         <v>0.99999654293060303</v>
       </c>
       <c r="E7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F7" s="1">
         <v>136489.69499999998</v>
@@ -961,14 +961,14 @@
     <row r="8">
       <c r="A8" s="1"/>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1">
         <v>0.99999892711639404</v>
       </c>
       <c r="E8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F8" s="1">
         <v>407213.54200000002</v>
@@ -977,7 +977,7 @@
     <row r="9">
       <c r="A9" s="1"/>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1">

--- a/input_data/admin_data/ECU/_clean/total-pre-ECU.xlsx
+++ b/input_data/admin_data/ECU/_clean/total-pre-ECU.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="97">
   <si>
     <t>year</t>
   </si>
